--- a/INSTANCES/instances_xlsx/A_MTN_2/136FL_5A_4.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_2/136FL_5A_4.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Parameters" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="M_stations" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Aircrafts" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Coefficients" r:id="rId8" sheetId="5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="112">
   <si>
     <t xml:space="preserve">YEAR</t>
   </si>
@@ -281,6 +282,84 @@
   </si>
   <si>
     <t>TK_DAY</t>
+  </si>
+  <si>
+    <t>FH_TK_MIN</t>
+  </si>
+  <si>
+    <t>FH_TK_MAX</t>
+  </si>
+  <si>
+    <t>FH_TK_MEDIAN</t>
+  </si>
+  <si>
+    <t>FH_TK_MEAN</t>
+  </si>
+  <si>
+    <t>FH_DAY_MIN</t>
+  </si>
+  <si>
+    <t>FH_DAY_MAX</t>
+  </si>
+  <si>
+    <t>FH_DAY_MEDIAN</t>
+  </si>
+  <si>
+    <t>FH_DAY_MEAN</t>
+  </si>
+  <si>
+    <t>TK_DAY_MIN</t>
+  </si>
+  <si>
+    <t>TK_DAY_MAX</t>
+  </si>
+  <si>
+    <t>TK_DAY_MEDIAN</t>
+  </si>
+  <si>
+    <t>TK_DAY_MEAN</t>
+  </si>
+  <si>
+    <t>TAIL_NUMBER</t>
+  </si>
+  <si>
+    <t>INIT_AIRPORT</t>
+  </si>
+  <si>
+    <t>INIT_FLYING_TIME</t>
+  </si>
+  <si>
+    <t>INIT_TAKEOFF</t>
+  </si>
+  <si>
+    <t>INIT_FLYING_DAY</t>
+  </si>
+  <si>
+    <t>N607AS</t>
+  </si>
+  <si>
+    <t>ANC</t>
+  </si>
+  <si>
+    <t>N585AS</t>
+  </si>
+  <si>
+    <t>N317AS</t>
+  </si>
+  <si>
+    <t>FAI</t>
+  </si>
+  <si>
+    <t>N587AS</t>
+  </si>
+  <si>
+    <t>JNU</t>
+  </si>
+  <si>
+    <t>N284AK</t>
+  </si>
+  <si>
+    <t>PHX</t>
   </si>
 </sst>
 </file>
@@ -4856,104 +4935,104 @@
   <sheetFormatPr defaultColWidth="10.62109375" defaultRowHeight="15.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" spans="1:5" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A1" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B1" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>73</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>74</v>
-      </c>
-      <c r="E1" t="s" s="0">
-        <v>75</v>
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="1:5" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A2" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C2" t="n" s="0">
+      <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="n" s="0">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n" s="0">
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A3" t="s" s="0">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>10</v>
-      </c>
-      <c r="C3" t="n" s="0">
+      <c r="A3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3">
         <v>3459</v>
       </c>
-      <c r="D3" t="n" s="0">
+      <c r="D3">
         <v>29</v>
       </c>
-      <c r="E3" t="n" s="0">
+      <c r="E3">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A4" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="B4" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="C4" t="n" s="0">
+      <c r="A4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="n" s="0">
-        <v>1</v>
-      </c>
-      <c r="E4" t="n" s="0">
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A5" t="s" s="0">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n" s="0">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5">
         <v>2500</v>
       </c>
-      <c r="D5" t="n" s="0">
+      <c r="D5">
         <v>21</v>
       </c>
-      <c r="E5" t="n" s="0">
+      <c r="E5">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" hidden="false" customFormat="false" ht="15.75" customHeight="false" collapsed="false" outlineLevel="0">
-      <c r="A6" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="C6" t="n" s="0">
+      <c r="A6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" t="n" s="0">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n" s="0">
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
@@ -4966,4 +5045,90 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E1" t="s">
+        <v>90</v>
+      </c>
+      <c r="F1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G1" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" t="s">
+        <v>96</v>
+      </c>
+      <c r="L1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>377</v>
+      </c>
+      <c r="C2">
+        <v>154</v>
+      </c>
+      <c r="D2">
+        <v>168</v>
+      </c>
+      <c r="E2">
+        <v>229</v>
+      </c>
+      <c r="F2">
+        <v>1079</v>
+      </c>
+      <c r="G2">
+        <v>676</v>
+      </c>
+      <c r="H2">
+        <v>651</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>